--- a/src/ii_skills/shared/excel_templates/17_track_record.xlsx
+++ b/src/ii_skills/shared/excel_templates/17_track_record.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,10 +29,21 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="0001395D"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
     </font>
   </fonts>
   <fills count="4">
@@ -44,8 +55,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A4A4A"/>
-        <bgColor rgb="004A4A4A"/>
+        <fgColor rgb="0001395D"/>
+        <bgColor rgb="0001395D"/>
       </patternFill>
     </fill>
     <fill>
@@ -67,14 +78,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -149,152 +161,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>FFO Per Unit Track Record</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Track_Record'!B1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Track_Record'!$A$2:$A$18</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Track_Record'!$B$2:$B$18</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Year</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>FFO Per Unit ($)</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5400000" cy="2700000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -586,268 +452,175 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1"/>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Historical FFO Per Unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>FFO_Per_Unit</t>
+          <t>FFO/Unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Distribution</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>SUMMARY METRICS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>2009</v>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Start Value</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>$0.42</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2010</v>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>End Value</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>$3.32</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2011</v>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>CAGR</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>10.0%</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2012</v>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2009-2025</t>
-        </is>
-      </c>
-    </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0.75</v>
+      <c r="B6" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>1.12</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>2014</v>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>0.9</v>
+      <c r="B7" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1.26</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>1.08</v>
+      <c r="B8" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>1.42</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>2016</v>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>1.3</v>
+      <c r="B9" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>1.55</v>
+      <c r="B10" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>1.75</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>1.65</v>
+      <c r="B11" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>1.9</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>1.78</v>
+      <c r="B12" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>2.07</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>1.92</v>
+      <c r="B13" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>2.21</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>2.05</v>
+      <c r="B14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>2.38</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>2.28</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>2.38</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
+      <c r="B15" t="n">
         <v>2025</v>
       </c>
-      <c r="B18" s="3" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>2.5</v>
+      <c r="C15" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>2.58</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>